--- a/data/source/2026-09-28/BSR_ES_Wet-Dry-Floor-Washer_Top50_2026-09-28.xlsx
+++ b/data/source/2026-09-28/BSR_ES_Wet-Dry-Floor-Washer_Top50_2026-09-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="209">
   <si>
     <t>#</t>
   </si>
@@ -232,88 +232,403 @@
     <t>B0D2KT41N3</t>
   </si>
   <si>
-    <t>https://www.amazon.esundefined</t>
-  </si>
-  <si>
-    <t>Cecotec Aspiradora con Cable en Seco y Húmedos - Aspirador Sólidos y Líquidos 16L Conga Rockstar Wet &amp; Dry Compact Garden Plu</t>
+    <t>Tamaño: 16 L</t>
+  </si>
+  <si>
+    <t>Marca: Cecotec | Función especial: Húmedo/seco | Tipo de filtro: Sistema de filtración doble | Recomendación de superficie: Todos los suelos | Fuente de alimentación: Eléctrico con cable | Voltaje: 1200 Voltios | Componentes incluidos: 1 x Aspiradora; 1 x Accesorio para esquinas; 1 x Accesorio 2 en 1; 1 x Base de aspiración universal; 1 x Cargador; 1 x Cepillo para el suelo; 1 x Manual de instrucciones; 1 x Tubo extensible; 1 x Tubo flexible | ¿Es inalámbrico?: No | Peso del producto: 4,5 Kilogramos | Capacidad: 16 litros</t>
+  </si>
+  <si>
+    <t>Cecotec</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/stores/Cecotec/page/8A5D1609-A164-427A-9580-48312AC42537?lp_asin=B0D2KT41N3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
+    <t>Cecotec Aspiradora con Cable en Seco y Húmedos - Aspirador Sólidos y Líquidos 16L Conga Rockstar Wet &amp; Dry Compact Garden Plus. 1200W, Ligero, Compacto, Doble Función de Succión y Soplado, Accesorios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aspirador de sólidos y líquidos de gran potencia con tanque de plástico para aspirar todo tipo de suciedad, incluidos líquidos, de cualquier rincón de tu hogar.
+Aspira sin esfuerzo gracias a su potencia de 1200 W y a su reducido peso y tamaño.
+Sistema de doble filtrado que filtra el agua y purifica el aire reteniendo de forma eficaz un gran porcentaje de alérgenos. Incluye función sopladora Blowing System.
+Gran radio de acción con más de 5 metros y porta accesorios para poder limpiar de la forma más cómoda hasta el último rincón.
+Incluye 4 accesorios para limpiar cualquier superficie de forma eficaz.</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0D2KT41N3?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/71zwr1xxvzL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://images-na.ssl-images-amazon.com/images/I/71zwr1xxvzL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0D33D9J3P</t>
+  </si>
+  <si>
+    <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras:Aspiradoras domésticas para sólidos y líquidos</t>
+  </si>
+  <si>
+    <t>Hogar y cocina</t>
+  </si>
+  <si>
+    <t>Aspiradoras domésticas para sólidos y líquidos</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>2024-04-25</t>
+  </si>
+  <si>
+    <t>AMZ</t>
+  </si>
+  <si>
+    <t>16天</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>4,5 Kilogramos</t>
+  </si>
+  <si>
+    <t>4.50 kg</t>
+  </si>
+  <si>
+    <t>38l. x 33an. x 45al. centímetros</t>
+  </si>
+  <si>
+    <t>5.37 kg</t>
+  </si>
+  <si>
+    <t>40 x 36 x 36 cm</t>
+  </si>
+  <si>
+    <t>40.00 x 36.00 x 36.00 cm</t>
+  </si>
+  <si>
+    <t>轻型标准大件</t>
+  </si>
+  <si>
+    <t>B0FR44ZBJP</t>
+  </si>
+  <si>
+    <t>Nombre de estilo: X-CLEAN 10 + Filtro</t>
+  </si>
+  <si>
+    <t>Marca: Rowenta | Función especial: Inalámbrico, Ligero | Tipo de filtro: Cartucho | Recomendación de superficie: Pisos duros sellados | Fuente de alimentación: Batería | Voltaje: 21,6 Voltios | Componentes incluidos: Base de carga, cepillo de limpieza, rodillo adicional, filtro adicional | ¿Es inalámbrico?: Sí | Peso del producto: 4,15 Kilogramos | Vataje: 200 vatios</t>
+  </si>
+  <si>
+    <t>Rowenta</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/stores/ROWENTA/page/3D429753-5927-4DBC-8D40-68488A481BD0?lp_asin=B0FR44ZBJP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
+    <t>Rowenta X-Clean 10, Aspiradora Fregona Eléctrica Sin Cable, Filtro Extra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ÓPTIMOS RESULTADOS: una fregona sin cable con tecnología Wet &amp; Dry que aspira y friega en una sola pasada, para una solución de limpieza todo en uno que ahorra tiempo y cubre cada centímetro de tu hogar
+LIMPIEZA SIN ESFUERZO: sistema de rodillo autopropulsado de Narwal para una fregona inalambrica ultraligera que solo pesa 0,8 kg en la mano, con un diseño flexible de 180 grados para un alcance máximo
+GRAN AUTONOMÍA: hasta 60 minutos con una sola carga, pensada tanto para derrames inesperados como para una limpieza a fondo
+SISTEMA DE AUTOLIMPIEZA: exclusivo sistema bidireccional de autolimpieza y autosecado sin complicaciones de Narwal con solo pulsar un botón, para que la fregona esté siempre limpia, seca y lista para funcionar
+TECNOLOGÍA DE VANGUARDIA: soluciones innovadoras que facilitan la limpieza, como instrucciones por voz, controles fáciles de usar con pantalla led, seguimiento de la suciedad en tiempo real y mucho más
+REDUCCIÓN INTELIGENTE DEL RUIDO: tecnología avanzada de amortiguación del ruido para que todos los aspectos del uso sean más silenciosos y menos molestos, desde la limpieza hasta el ciclo de autolavado
+RODILLO SIN ENREDOS: limpieza sin complicaciones con un rodillo de microfibra que no se enreda, diseñado para no obstruir el pelo largo ni el pelo de las mascotas, para una limpieza más suave y fácil
+DETALLES BIEN ELABORADOS: desde la estética elegante hasta la filtración en 2 fases y la ergonomía avanzada, descubre una fregona inalambrica diseñada para facilitar la limpieza hasta el más mínimo detalle
+5 MODOS DE LIMPIEZA: Modo Auto/IA: ajuste automático del caudal de agua y de la potencia de aspiración en función del nivel de suciedad detectado por el sensor inteligente. Modo fregado: para eliminar el agua superficial. Modo silencioso: experiencia sin ruidos, para suelos no muy sucios. Modo Turbo : para manchas incrustadas y que se necesite mayor caudal de agua. Modo Max: para las manchas más difíciles
+¿QUÉ HAY EN LA CAJA?: fregona sin cable Wet &amp; Dry, base de carga para ciclo de autolavado y autosecado, cepillo de limpieza, cargador, rodillo adicional, filtro adicional</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/dp/B0FR44ZBJP?psc=1</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/317fxQNFv3L._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0H633WR96</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>4天</t>
+  </si>
+  <si>
+    <t>Opción Amazon</t>
+  </si>
+  <si>
+    <t>4,15 Kilogramos</t>
+  </si>
+  <si>
+    <t>4.15 kg</t>
+  </si>
+  <si>
+    <t>27l. x 23an. x 116al. centímetros</t>
+  </si>
+  <si>
+    <t>6.56 kg</t>
+  </si>
+  <si>
+    <t>73.3 x 33.3 x 27.4 cm</t>
+  </si>
+  <si>
+    <t>73.30 x 33.30 x 27.40 cm</t>
   </si>
   <si>
     <t>B0FR4TKY99</t>
   </si>
   <si>
-    <t>Rowenta X-Clean 2, Aspiradora Fregona Eléctrica Sin Cable, Azul AquasTecnología Wet &amp; Dry, Autolimpieza, Aspira y friega, M</t>
+    <t>Nombre de estilo: X-CLEAN 2 Azul Aqua</t>
+  </si>
+  <si>
+    <t>Marca: Rowenta | Función especial: Wet &amp; Dry, Autolimpieza, Aspira y friega, Limpieza de Bordes, Modos Eco/MAX | Tipo de filtro: espuma, tela | Recomendación de superficie: Pisos duros sellados, superficies domésticas generales | Fuente de alimentación: Batería | Componentes incluidos: Cabezal de fregado, Depósito de agua | ¿Es inalámbrico?: Sí | Peso del producto: 5 Kilogramos | Vataje: 120 vatios | Usos recomendados para el producto: Pisos duros sellados, superficies domésticas generales</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/stores/ROWENTA/page/3D429753-5927-4DBC-8D40-68488A481BD0?lp_asin=B0FR4TKY99&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
+    <t>Rowenta X-Clean 2, Aspiradora Fregona Eléctrica Sin Cable, Azul Aqua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMPIEZA 2 EN 1: friega y aspira residuos húmedos y secos gracias a los modos ECO/MAX, con un flujo constante de agua limpia para una limpieza eficaz
+LIMPIEZA SIN ESFUERZO: rodillo autopropulsado de 1,1 kg y asa trasera ergonómica para facilitar el transporte
+RENDIMIENTO MEJORADO: la limpieza de bordes rastrea el polvo a lo largo de las paredes y muebles, con un caudal de agua optimizado para una limpieza impecable y un secado más rápido
+MANTENIMIENTO SIMPLIFICADO: ciclo de autolimpieza de 90 segundos con un solo clic para tener el rodillo siempre limpio, con rodillo adicional para una limpieza ininterrumpida
+15 AÑOS DE REPARABILIDAD A UN PRECIO JUSTO: para una mayor durabilidad, recomendamos hacer las reparaciones en nuestra red de 6200 centros de reparación en todo el mundo</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0FR4TKY99?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/61WbHpxBXeL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/31vRNmHmuqL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0H63F8TQZ</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2025-09-21</t>
+  </si>
+  <si>
+    <t>3天</t>
+  </si>
+  <si>
+    <t>5 Kilogramos</t>
+  </si>
+  <si>
+    <t>5.00 kg</t>
+  </si>
+  <si>
+    <t>28l. x 21an. x 115al. centímetros</t>
+  </si>
+  <si>
+    <t>7.29 kg</t>
+  </si>
+  <si>
+    <t>75.2 x 33.7 x 29 cm</t>
+  </si>
+  <si>
+    <t>75.20 x 33.70 x 29.00 cm</t>
   </si>
   <si>
     <t>B0DJ7LFXC6</t>
   </si>
   <si>
-    <t>roborock F25 XT Aspiradora-Fregona Sin Cable en Seco y Húmedo, 20.000 PasAutolimpieza y Secado Rápido a 90°C, Diseño Plano</t>
+    <t>Modelo: F25 XT</t>
+  </si>
+  <si>
+    <t>Marca: roborock | Función especial: Filtro lavable | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Suelo duro, alfombra | Fuente de alimentación: Batería | Voltaje: 120 Voltios | Componentes incluidos: 1 cable de alimentación, 1 cepillo de limpieza, 1 manual de instrucciones (idioma español no idioma español no garantizado), 1 roborock aspiradora F25 XT, Base de carga | ¿Es inalámbrico?: Sí | Peso del producto: 10,3 Libras | Capacidad: 740 miligramos</t>
+  </si>
+  <si>
+    <t>roborock</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/stores/roborock/page/650F9802-6540-4D28-BB83-5B16C939885D?lp_asin=B0DJ7LFXC6&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
+    <t>roborock F25 XT Aspiradora-Fregona Sin Cable en Seco y Húmedo, 20.000 Pa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tecnología de dos rascadores para un menor esfuerzo: ¡olvídate de los enredos de pelo y de las marcas de agua! Nuestro revolucionario sistema de dos rascadores garantiza un acabado perfecto sin excepciones: con el elegante rascador plano que aporta un control perfecto del agua y el ingenioso diseño de peine que atrapa el pelo sin esfuerzo, el suelo queda siempre inmaculado. Además, gracias a las certificaciones de SGS y TÜV, podrás estar tranquilo sabiendo que los enredos son cosa del pasado.
+Aspiración potente y limpieza versátil: transforma tu rutina de limpieza con la impresionante potencia de aspiración de 20 000 Pa. Ya sea que tengas que limpiar accidentes de mascotas, bebidas derramadas o la suciedad diaria, esta aspiradora-fregona puede lidiar con todo sin problema. Y al poder colocarla en posición horizontal, podrás limpiar bajo los muebles sin esfuerzo para eliminar la suciedad de hasta el último rincón.
+Autolimpieza a alta temperatura: ¡descubre la magia de la autolimpieza! Nuestra aspiradora en seco y húmedo elimina la grasa y la suciedad, mientras que el frotado bidireccional garantiza que quede totalmente limpia. Con el secado rápido a 90 °C y dos modos entre los que elegir (rápido en 5 minutos o silencioso en 20 minutos), podrás volver a disfrutar de un espacio limpio antes de que te des cuenta.
+Diseño flexible y fácil de usar: ¡limpiar ya no tiene que ser una tarea! El cabezal de nuestra aspiradora en seco y húmedo tiene una capacidad de giro de 70°, de modo que se desliza fácilmente alrededor de los muebles. Además, el depósito de agua estratégicamente colocado en una posición más baja cambia el peso para un uso sin esfuerzo. Y las ruedas con asistencia basada en IA se deslizan con fluidez por todas las superficies, haciendo que cada sesión de limpieza sea coser y cantar.
+Detección inteligente de suciedad: ¡deja que la tecnología trabaje por ti! Nuestra aspiradora en húmedo para suelos duros está equipada con un sensor inteligente de detección de suciedad que ajusta automáticamente la potencia de aspiración en función del nivel de suciedad, de modo que garantiza siempre la mejor limpieza. Con tan solo pulsar un botón, podrás eliminar cualquier tipo de suciedad con confianza y facilidad.
+Limpieza de tres bordes: ¡evita que la suciedad se acumule en las esquinas! Nuestro combo de aspiradora y fregona llega justo hasta el borde con un margen de menos de 1 mm, lo que resulta ideal para limpiar rodapiés, escaleras y esquinas. Incluso es capaz de dispensar la solución de limpieza automáticamente para que puedas conseguir un acabado reluciente sin esfuerzo.</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0DJ7LFXC6?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/71kF7U4CGSL._AC_UL300_SR300,200_.jpg</t>
-  </si>
-  <si>
-    <t>B0FR44ZBJP</t>
-  </si>
-  <si>
-    <t>Rowenta X-Clean 10, Aspiradora Fregona Eléctrica Sin Cable, Filtro ExtrasTecnología Wet &amp; Dry y Dual Edge, Autolimpieza y S</t>
-  </si>
-  <si>
-    <t>https://www.amazon.es/dp/B0FR44ZBJP?psc=1</t>
-  </si>
-  <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/619yApMYqML._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/41vgb56JNJL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0HDCGG5PJ</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>10,3 Libras</t>
+  </si>
+  <si>
+    <t>4.67 kg</t>
+  </si>
+  <si>
+    <t>35,2l. x 31,6an. x 115,7al. centímetros</t>
+  </si>
+  <si>
+    <t>8.28 kg</t>
+  </si>
+  <si>
+    <t>73 x 33 x 30 cm</t>
+  </si>
+  <si>
+    <t>73.00 x 33.00 x 30.00 cm</t>
   </si>
   <si>
     <t>B0DGV9F4X3</t>
   </si>
   <si>
-    <t>Rowenta X-Clean 4, Aspiradora Fregona Eléctrica Sin Cable, NegrosAspira y Friega a la vez, 200 W, Pantalla De Control Intel</t>
+    <t>Nombre de estilo: X-CLEAN 4 Negro</t>
+  </si>
+  <si>
+    <t>Marca: Rowenta | Función especial: Inalámbrico | Tipo de filtro: Filtro de espuma, Filtro HEPA | Recomendación de superficie: Parquet, Mármol, Laminado, Azulejos | Fuente de alimentación: Batería | Voltaje: 18,5 Voltios | Componentes incluidos: Rodillo suave, rodillo recurrente, filtro tipo HEPA adicional, filtro de espuma adicional, cepillo de limpieza con función colador y función cortador | ¿Es inalámbrico?: Sí | Peso del producto: 5,4 Kilogramos | Capacidad: 1,1 litros</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/stores/ROWENTA/page/3D429753-5927-4DBC-8D40-68488A481BD0?lp_asin=B0DGV9F4X3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
+    <t>Rowenta X-Clean 4, Aspiradora Fregona Eléctrica Sin Cable, Negro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMPIEZA 2 EN 1: fregona eléctricainalámbrica para limpieza seca y húmeda que permite ganar tiempo aspirando y fregando enuna sola pasada, para unos resultados óptimos en todo tipo de suelos duros (madera, mármol, laminados y baldosas)
+DETECCIÓN INTELIGENTE DE LA SUCIEDAD: detección automática de la suciedad con indicadores de color en una pantalla led (rojo para la suciedad y azul cuando detecta un suelo limpio) y un ajuste automático de la velocidad de rotación del rodillo y del flujo de agua para conseguir unos óptimosresultados
+GRAN AUTONOMÍA: limpieza sin cables que marca la diferencia, con hasta 50min de autonomía para cubrir hasta 350m²dependiendo del mobiliario de la casa
+LIMPIEZA SIN ESFUERZO:diseño moderno, ligero, tan solo 1,1kg en tu mano, inteligente,con un sistema de rodillos ayudados por las ruedas, siendo necesario utilizar solo un 25 %del esfuerzo habitual
+SISTEMA DE AUTOLIMPIEZA:activa la función con tan solo pulsar un botón y, una vez lavado el rodillo, solo tienes que dejarlopreviamente secarpara que esté listo para la siguiente sesión de limpieza mientras se carga en la base</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0DGV9F4X3?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/61ZOUuPZaJL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://images-na.ssl-images-amazon.com/images/I/61ZOUuPZaJL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0DKMVFHRN</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>2024-11-07</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>5,4 Kilogramos</t>
+  </si>
+  <si>
+    <t>5.40 kg</t>
+  </si>
+  <si>
+    <t>31,5l. x 30,5an. x 114,7al. centímetros</t>
+  </si>
+  <si>
+    <t>7.52 kg</t>
+  </si>
+  <si>
+    <t>75.8 x 33 x 28.8 cm</t>
+  </si>
+  <si>
+    <t>75.80 x 33.00 x 28.80 cm</t>
   </si>
   <si>
     <t>B0H9LVZZV1</t>
   </si>
   <si>
-    <t>Bosch Fregona aspiradora eléctrica 2 en 1, BHF41WS, sin Cable, BlancosAspira y friega de una pasada, autolimpieza, sistema</t>
+    <t>Marca: Bosch | Voltaje: 240 Voltios | Peso del producto: 8,5 Kilogramos | Vataje: 250 vatios | Factor de forma: Palo | Color: Blanco | Dimensiones del producto: 35,9l. x 30,4an. x 115,8al. centímetros | Descripción de la pila: Iones de litio | Nivel de ruido: 78 Decibelios | Fabricante: BSH Hausgeräte GmbH</t>
+  </si>
+  <si>
+    <t>Bosch</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/stores/BoschElectrodom%C3%A9sticos/page/2DDBCCDF-87B9-4E0B-94C6-713ED28E8982?lp_asin=B0H9LVZZV1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
+    <t>Bosch Fregona aspiradora eléctrica 2 en 1, BHF41WS, sin Cable, Blanco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHORRA TIEMPO CON LIMPIEZA 2 EN 1: aspira y friega de una pasada y en la mitad de tiempo, en comparación con el tradicional aspirado y fregado (basado en pruebas internas en comparación con el aspirado y fregado tradicionales)
+ACABA CON LA SUCIEDAD DIARIA: elimina el polvo, la suciedad y los líquidos en una sola pasada con una fuerte succión, una potente presión de fregado y el agua sucia recogida en un depósito separado
+MANTÉN LOS SUELOS LIMPIOS, UNIFORMES Y SIN MARCAS: el sistema automático escurre el agua sucia del rodillo mientras se suministra agua limpia continuamente, ayudando a conseguir resultados de calidad
+RELÁJATE GRACIAS A UN MANTENIMIENTO SIN ESFUERZO: ahorra tiempo después de cada tarea con la limpieza con agua caliente, la autolimpieza, el secado con aire caliente y el sistema antienredos de pelo
+CONTENIDO DE ENVÍO: Fregona aspiradora con mango ergonómico, filtro, cepillo de limpieza y batería potente</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0H9LVZZV1?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/51LLsijMWXL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://images-na.ssl-images-amazon.com/images/I/51LLsijMWXL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>8,5 Kilogramos</t>
+  </si>
+  <si>
+    <t>8.50 kg</t>
+  </si>
+  <si>
+    <t>35,9l. x 30,4an. x 115,8al. centímetros</t>
+  </si>
+  <si>
+    <t>10.51 kg</t>
+  </si>
+  <si>
+    <t>79 x 34 x 32 cm</t>
+  </si>
+  <si>
+    <t>79.00 x 34.00 x 32.00 cm</t>
   </si>
   <si>
     <t>B0H9LQCPJ9</t>
   </si>
   <si>
-    <t>Bosch Fregona aspiradora eléctrica 2 en 1, BHF61BS, sin Cable, en NegrosAspira y friega en una sola pasada eliminando sucie</t>
+    <t>Marca: Bosch | Voltaje: 240 Voltios | Peso del producto: 8,5 Kilogramos | Color: Negro | Dimensiones del producto: 35,9l. x 30,4an. x 115,8al. centímetros | Descripción de la pila: Iones de litio | Nivel de ruido: 78 Decibelios | Fabricante: BSH Hausgeräte GmbH | Número de productos: 1</t>
+  </si>
+  <si>
+    <t>https://www.amazon.es/stores/BoschElectrodom%C3%A9sticos/page/2DDBCCDF-87B9-4E0B-94C6-713ED28E8982?lp_asin=B0H9LQCPJ9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
+    <t>Bosch Fregona aspiradora eléctrica 2 en 1, BHF61BS, sin Cable, en Negro</t>
   </si>
   <si>
     <t>https://www.amazon.es/dp/B0H9LQCPJ9?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/61i3ER7HQGL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/31jEuvrw7oL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
   <si>
     <t>导出时自动对相同ASIN去重。可能导致导出的产品总数与页面显示数量不一致</t>
@@ -329,9 +644,6 @@
   </si>
   <si>
     <t>市场份额</t>
-  </si>
-  <si>
-    <t>未知品牌</t>
   </si>
   <si>
     <t>卖家</t>
@@ -503,11 +815,11 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -573,13 +885,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -617,13 +929,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -705,13 +1017,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -749,13 +1061,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1514,7 +1826,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="2" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A2" s="13">
         <v>1</v>
       </c>
@@ -1525,90 +1837,124 @@
         <v>71</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>70</v>
+        <v>73</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>74</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="M2" s="1"/>
+        <v>80</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N2" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q2" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O2" s="15">
+        <v>3722</v>
+      </c>
+      <c r="P2" s="15">
+        <v>-898</v>
+      </c>
+      <c r="Q2" s="16">
+        <v>-0.77</v>
       </c>
       <c r="R2" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S2" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U2" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V2" s="15" t="s">
-        <v>70</v>
+        <v>84</v>
+      </c>
+      <c r="T2" s="15">
+        <v>519</v>
+      </c>
+      <c r="U2" s="16">
+        <v>1.28</v>
+      </c>
+      <c r="V2" s="15">
+        <v>23303</v>
       </c>
       <c r="W2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="X2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z2" s="19">
+        <v>85</v>
+      </c>
+      <c r="X2" s="15">
+        <v>12018</v>
+      </c>
+      <c r="Y2" s="19">
+        <v>2</v>
+      </c>
+      <c r="Z2" s="20">
         <v>37.11</v>
       </c>
-      <c r="AD2" s="20">
-        <v>943</v>
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="2"/>
+      <c r="AD2" s="19">
+        <v>944</v>
+      </c>
+      <c r="AE2" s="15">
+        <v>45</v>
       </c>
       <c r="AF2" s="21">
         <v>3.8</v>
       </c>
       <c r="AG2" s="22">
-        <v>0</v>
+        <v>0.0867</v>
+      </c>
+      <c r="AH2" s="20">
+        <v>10.1</v>
       </c>
       <c r="AI2" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK2" s="1"/>
-      <c r="AL2" s="20" t="s">
-        <v>70</v>
+        <v>0.63</v>
+      </c>
+      <c r="AK2" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL2" s="19">
+        <v>886</v>
+      </c>
+      <c r="AM2" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="AN2" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="AO2" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ2" s="20" t="s">
-        <v>70</v>
+      <c r="AP2" s="20">
+        <v>69.35</v>
+      </c>
+      <c r="AQ2" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR2" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS2" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT2" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="AU2" s="13" t="s">
         <v>70</v>
@@ -1620,7 +1966,7 @@
         <v>70</v>
       </c>
       <c r="AX2" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AY2" s="13" t="s">
         <v>70</v>
@@ -1635,16 +1981,16 @@
         <v>70</v>
       </c>
       <c r="BC2" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BD2" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BE2" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF2" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BG2" s="13" t="s">
         <v>70</v>
@@ -1652,20 +1998,35 @@
       <c r="BH2" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ2" s="23" t="s">
+        <v>91</v>
+      </c>
       <c r="BK2" s="23" t="s">
-        <v>70</v>
+        <v>92</v>
+      </c>
+      <c r="BL2" s="23" t="s">
+        <v>93</v>
       </c>
       <c r="BM2" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN2" s="23" t="s">
+        <v>94</v>
+      </c>
       <c r="BO2" s="23" t="s">
-        <v>70</v>
+        <v>94</v>
+      </c>
+      <c r="BP2" s="23" t="s">
+        <v>95</v>
       </c>
       <c r="BQ2" s="23" t="s">
-        <v>70</v>
+        <v>96</v>
+      </c>
+      <c r="BR2" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="3" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" s="13">
         <v>2</v>
       </c>
@@ -1673,59 +2034,64 @@
         <v>70</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>70</v>
+        <v>100</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>101</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="M3" s="1"/>
+        <v>107</v>
+      </c>
+      <c r="M3" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N3" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q3" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O3" s="15">
+        <v>13679</v>
+      </c>
+      <c r="P3" s="15">
+        <v>2194</v>
+      </c>
+      <c r="Q3" s="16">
+        <v>0.06</v>
       </c>
       <c r="R3" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S3" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U3" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V3" s="15" t="s">
-        <v>70</v>
+        <v>108</v>
+      </c>
+      <c r="T3" s="15">
+        <v>54</v>
+      </c>
+      <c r="U3" s="16">
+        <v>0.79</v>
+      </c>
+      <c r="V3" s="15">
+        <v>21599</v>
       </c>
       <c r="W3" s="15" t="s">
         <v>70</v>
@@ -1733,33 +2099,62 @@
       <c r="X3" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z3" s="19">
-        <v>148.75</v>
-      </c>
-      <c r="AD3" s="20">
-        <v>133</v>
+      <c r="Y3" s="19">
+        <v>3</v>
+      </c>
+      <c r="Z3" s="20">
+        <v>330.57</v>
+      </c>
+      <c r="AA3" s="4"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="2"/>
+      <c r="AD3" s="19">
+        <v>132</v>
+      </c>
+      <c r="AE3" s="15">
+        <v>27</v>
       </c>
       <c r="AF3" s="21">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AG3" s="22">
-        <v>0</v>
+        <v>0.5</v>
+      </c>
+      <c r="AH3" s="20">
+        <v>11.23</v>
       </c>
       <c r="AI3" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK3" s="1"/>
-      <c r="AL3" s="20" t="s">
-        <v>70</v>
+        <v>0.83</v>
+      </c>
+      <c r="AK3" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="AL3" s="19">
+        <v>355</v>
+      </c>
+      <c r="AM3" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="AN3" s="13" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AO3" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ3" s="20" t="s">
-        <v>70</v>
+      <c r="AP3" s="20">
+        <v>105.32</v>
+      </c>
+      <c r="AQ3" s="19">
+        <v>9</v>
+      </c>
+      <c r="AR3" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS3" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT3" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="AU3" s="13" t="s">
         <v>70</v>
@@ -1774,7 +2169,7 @@
         <v>70</v>
       </c>
       <c r="AY3" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AZ3" s="13" t="s">
         <v>70</v>
@@ -1786,37 +2181,55 @@
         <v>70</v>
       </c>
       <c r="BC3" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BD3" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BE3" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF3" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BG3" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BH3" s="14" t="s">
-        <v>70</v>
+        <v>90</v>
+      </c>
+      <c r="BI3" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="BJ3" s="23" t="s">
+        <v>112</v>
       </c>
       <c r="BK3" s="23" t="s">
-        <v>70</v>
+        <v>113</v>
+      </c>
+      <c r="BL3" s="23" t="s">
+        <v>114</v>
       </c>
       <c r="BM3" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN3" s="23" t="s">
+        <v>115</v>
+      </c>
       <c r="BO3" s="23" t="s">
-        <v>70</v>
+        <v>115</v>
+      </c>
+      <c r="BP3" s="23" t="s">
+        <v>116</v>
       </c>
       <c r="BQ3" s="23" t="s">
-        <v>70</v>
+        <v>117</v>
+      </c>
+      <c r="BR3" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="4" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A4" s="13">
         <v>3</v>
       </c>
@@ -1824,59 +2237,64 @@
         <v>70</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>70</v>
+        <v>120</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>101</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="H4" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="M4" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="I4" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="J4" s="14" t="s">
+      <c r="N4" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="O4" s="15">
+        <v>14602</v>
+      </c>
+      <c r="P4" s="15">
+        <v>-5384</v>
+      </c>
+      <c r="Q4" s="16">
+        <v>-0.14</v>
+      </c>
+      <c r="R4" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="L4" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="M4" s="1"/>
-      <c r="N4" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O4" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P4" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q4" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="R4" s="17" t="s">
-        <v>70</v>
-      </c>
       <c r="S4" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T4" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U4" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V4" s="15" t="s">
-        <v>70</v>
+        <v>127</v>
+      </c>
+      <c r="T4" s="15">
+        <v>97</v>
+      </c>
+      <c r="U4" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="V4" s="15">
+        <v>14429</v>
       </c>
       <c r="W4" s="15" t="s">
         <v>70</v>
@@ -1884,33 +2302,62 @@
       <c r="X4" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z4" s="19">
-        <v>280.17</v>
-      </c>
-      <c r="AD4" s="20">
-        <v>604</v>
+      <c r="Y4" s="19">
+        <v>5</v>
+      </c>
+      <c r="Z4" s="20">
+        <v>148.75</v>
+      </c>
+      <c r="AA4" s="4"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="19">
+        <v>133</v>
+      </c>
+      <c r="AE4" s="15">
+        <v>15</v>
       </c>
       <c r="AF4" s="21">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AG4" s="22">
-        <v>0</v>
+        <v>0.15460000000000002</v>
+      </c>
+      <c r="AH4" s="20">
+        <v>11.58</v>
       </c>
       <c r="AI4" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="1"/>
-      <c r="AL4" s="20" t="s">
-        <v>70</v>
+        <v>0.8</v>
+      </c>
+      <c r="AK4" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="AL4" s="19">
+        <v>372</v>
+      </c>
+      <c r="AM4" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="AN4" s="13" t="s">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="AO4" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ4" s="20" t="s">
-        <v>70</v>
+      <c r="AP4" s="20">
+        <v>113.54</v>
+      </c>
+      <c r="AQ4" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR4" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS4" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT4" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="AU4" s="13" t="s">
         <v>70</v>
@@ -1925,7 +2372,7 @@
         <v>70</v>
       </c>
       <c r="AY4" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AZ4" s="13" t="s">
         <v>70</v>
@@ -1937,10 +2384,10 @@
         <v>70</v>
       </c>
       <c r="BC4" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BD4" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BE4" s="13" t="s">
         <v>70</v>
@@ -1952,22 +2399,40 @@
         <v>70</v>
       </c>
       <c r="BH4" s="14" t="s">
-        <v>70</v>
+        <v>90</v>
+      </c>
+      <c r="BI4" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="BJ4" s="23" t="s">
+        <v>130</v>
       </c>
       <c r="BK4" s="23" t="s">
-        <v>70</v>
+        <v>131</v>
+      </c>
+      <c r="BL4" s="23" t="s">
+        <v>132</v>
       </c>
       <c r="BM4" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN4" s="23" t="s">
+        <v>133</v>
+      </c>
       <c r="BO4" s="23" t="s">
-        <v>70</v>
+        <v>133</v>
+      </c>
+      <c r="BP4" s="23" t="s">
+        <v>134</v>
       </c>
       <c r="BQ4" s="23" t="s">
-        <v>70</v>
+        <v>135</v>
+      </c>
+      <c r="BR4" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="5" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
         <v>4</v>
       </c>
@@ -1975,59 +2440,64 @@
         <v>70</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>70</v>
+        <v>137</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>70</v>
+        <v>138</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>139</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>70</v>
+        <v>142</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>86</v>
+        <v>143</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>87</v>
+        <v>144</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="M5" s="1"/>
+        <v>145</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N5" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O5" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P5" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q5" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O5" s="15">
+        <v>1501</v>
+      </c>
+      <c r="P5" s="15">
+        <v>-345</v>
+      </c>
+      <c r="Q5" s="16">
+        <v>-0.28</v>
       </c>
       <c r="R5" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S5" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T5" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U5" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V5" s="15" t="s">
-        <v>70</v>
+        <v>146</v>
+      </c>
+      <c r="T5" s="15">
+        <v>693</v>
+      </c>
+      <c r="U5" s="16">
+        <v>0.75</v>
+      </c>
+      <c r="V5" s="15">
+        <v>194158</v>
       </c>
       <c r="W5" s="15" t="s">
         <v>70</v>
@@ -2035,33 +2505,62 @@
       <c r="X5" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z5" s="19">
-        <v>330.57</v>
-      </c>
-      <c r="AD5" s="20">
-        <v>132</v>
+      <c r="Y5" s="19">
+        <v>6</v>
+      </c>
+      <c r="Z5" s="20">
+        <v>280.17</v>
+      </c>
+      <c r="AA5" s="4"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="2"/>
+      <c r="AD5" s="19">
+        <v>604</v>
+      </c>
+      <c r="AE5" s="15">
+        <v>183</v>
       </c>
       <c r="AF5" s="21">
         <v>3.9</v>
       </c>
       <c r="AG5" s="22">
-        <v>0</v>
+        <v>0.2641</v>
+      </c>
+      <c r="AH5" s="20">
+        <v>11.58</v>
       </c>
       <c r="AI5" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="1"/>
-      <c r="AL5" s="20" t="s">
-        <v>70</v>
+        <v>0.81</v>
+      </c>
+      <c r="AK5" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="AL5" s="19">
+        <v>594</v>
+      </c>
+      <c r="AM5" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="AN5" s="13" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AO5" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ5" s="20" t="s">
-        <v>70</v>
+      <c r="AP5" s="20">
+        <v>111.95</v>
+      </c>
+      <c r="AQ5" s="19">
+        <v>9</v>
+      </c>
+      <c r="AR5" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS5" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT5" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="AU5" s="13" t="s">
         <v>70</v>
@@ -2076,7 +2575,7 @@
         <v>70</v>
       </c>
       <c r="AY5" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AZ5" s="13" t="s">
         <v>70</v>
@@ -2088,16 +2587,16 @@
         <v>70</v>
       </c>
       <c r="BC5" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BD5" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BE5" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF5" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BG5" s="13" t="s">
         <v>70</v>
@@ -2105,20 +2604,38 @@
       <c r="BH5" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BI5" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="BJ5" s="23" t="s">
+        <v>148</v>
+      </c>
       <c r="BK5" s="23" t="s">
-        <v>70</v>
+        <v>149</v>
+      </c>
+      <c r="BL5" s="23" t="s">
+        <v>150</v>
       </c>
       <c r="BM5" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN5" s="23" t="s">
+        <v>151</v>
+      </c>
       <c r="BO5" s="23" t="s">
-        <v>70</v>
+        <v>151</v>
+      </c>
+      <c r="BP5" s="23" t="s">
+        <v>152</v>
       </c>
       <c r="BQ5" s="23" t="s">
-        <v>70</v>
+        <v>153</v>
+      </c>
+      <c r="BR5" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="6" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A6" s="13">
         <v>5</v>
       </c>
@@ -2126,50 +2643,55 @@
         <v>70</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>88</v>
+        <v>154</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>70</v>
+        <v>156</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>101</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>72</v>
+        <v>157</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>89</v>
+        <v>158</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>70</v>
+        <v>159</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="M6" s="1"/>
+        <v>162</v>
+      </c>
+      <c r="M6" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N6" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O6" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P6" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q6" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O6" s="15">
+        <v>233022</v>
+      </c>
+      <c r="P6" s="15">
+        <v>-12404</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>-0.06</v>
       </c>
       <c r="R6" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S6" s="18" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="T6" s="15" t="s">
         <v>70</v>
@@ -2186,9 +2708,20 @@
       <c r="X6" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z6" s="4"/>
-      <c r="AD6" s="20">
-        <v>824</v>
+      <c r="Y6" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="20">
+        <v>173.74</v>
+      </c>
+      <c r="AA6" s="4"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="2"/>
+      <c r="AD6" s="19">
+        <v>825</v>
+      </c>
+      <c r="AE6" s="15">
+        <v>35</v>
       </c>
       <c r="AF6" s="21">
         <v>4.2</v>
@@ -2196,12 +2729,20 @@
       <c r="AG6" s="22">
         <v>0</v>
       </c>
+      <c r="AH6" s="20">
+        <v>11.58</v>
+      </c>
       <c r="AI6" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="1"/>
-      <c r="AL6" s="20" t="s">
-        <v>70</v>
+        <v>0.78</v>
+      </c>
+      <c r="AK6" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="AL6" s="19">
+        <v>689</v>
+      </c>
+      <c r="AM6" s="13" t="s">
+        <v>165</v>
       </c>
       <c r="AN6" s="13" t="s">
         <v>70</v>
@@ -2209,8 +2750,18 @@
       <c r="AO6" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ6" s="20" t="s">
-        <v>70</v>
+      <c r="AP6" s="4"/>
+      <c r="AQ6" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR6" s="19">
+        <v>2</v>
+      </c>
+      <c r="AS6" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT6" s="13" t="s">
+        <v>165</v>
       </c>
       <c r="AU6" s="13" t="s">
         <v>70</v>
@@ -2237,16 +2788,16 @@
         <v>70</v>
       </c>
       <c r="BC6" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BD6" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BE6" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF6" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BG6" s="13" t="s">
         <v>70</v>
@@ -2254,20 +2805,35 @@
       <c r="BH6" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ6" s="23" t="s">
+        <v>166</v>
+      </c>
       <c r="BK6" s="23" t="s">
-        <v>70</v>
+        <v>167</v>
+      </c>
+      <c r="BL6" s="23" t="s">
+        <v>168</v>
       </c>
       <c r="BM6" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN6" s="23" t="s">
+        <v>169</v>
+      </c>
       <c r="BO6" s="23" t="s">
-        <v>70</v>
+        <v>169</v>
+      </c>
+      <c r="BP6" s="23" t="s">
+        <v>170</v>
       </c>
       <c r="BQ6" s="23" t="s">
-        <v>70</v>
+        <v>171</v>
+      </c>
+      <c r="BR6" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="7" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A7" s="13">
         <v>6</v>
       </c>
@@ -2275,59 +2841,64 @@
         <v>70</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>92</v>
+        <v>172</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>70</v>
+        <v>173</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>174</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>72</v>
+        <v>175</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>93</v>
+        <v>176</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>70</v>
+        <v>177</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>94</v>
+        <v>178</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>95</v>
+        <v>179</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="M7" s="1"/>
+        <v>172</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N7" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O7" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P7" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q7" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O7" s="15">
+        <v>421247</v>
+      </c>
+      <c r="P7" s="15">
+        <v>-34487</v>
+      </c>
+      <c r="Q7" s="16">
+        <v>-6.13</v>
       </c>
       <c r="R7" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S7" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T7" s="15" t="s">
-        <v>70</v>
+        <v>180</v>
+      </c>
+      <c r="T7" s="15">
+        <v>9</v>
       </c>
       <c r="U7" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="V7" s="15" t="s">
-        <v>70</v>
+      <c r="V7" s="15">
+        <v>3591</v>
       </c>
       <c r="W7" s="15" t="s">
         <v>70</v>
@@ -2335,22 +2906,41 @@
       <c r="X7" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z7" s="4"/>
-      <c r="AD7" s="20">
+      <c r="Y7" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="20">
+        <v>399</v>
+      </c>
+      <c r="AA7" s="4"/>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="2"/>
+      <c r="AD7" s="19">
         <v>35</v>
+      </c>
+      <c r="AE7" s="15">
+        <v>2</v>
       </c>
       <c r="AF7" s="21">
         <v>4.3</v>
       </c>
       <c r="AG7" s="22">
-        <v>0</v>
+        <v>0.22219999999999998</v>
+      </c>
+      <c r="AH7" s="20">
+        <v>12.61</v>
       </c>
       <c r="AI7" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="1"/>
-      <c r="AL7" s="20" t="s">
-        <v>70</v>
+        <v>0.82</v>
+      </c>
+      <c r="AK7" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="AL7" s="19">
+        <v>48</v>
+      </c>
+      <c r="AM7" s="13" t="s">
+        <v>165</v>
       </c>
       <c r="AN7" s="13" t="s">
         <v>70</v>
@@ -2358,8 +2948,18 @@
       <c r="AO7" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ7" s="20" t="s">
-        <v>70</v>
+      <c r="AP7" s="4"/>
+      <c r="AQ7" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR7" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS7" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT7" s="13" t="s">
+        <v>165</v>
       </c>
       <c r="AU7" s="13" t="s">
         <v>70</v>
@@ -2386,7 +2986,7 @@
         <v>70</v>
       </c>
       <c r="BC7" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BD7" s="13" t="s">
         <v>70</v>
@@ -2403,17 +3003,32 @@
       <c r="BH7" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ7" s="23" t="s">
+        <v>182</v>
+      </c>
       <c r="BK7" s="23" t="s">
-        <v>70</v>
+        <v>183</v>
+      </c>
+      <c r="BL7" s="23" t="s">
+        <v>184</v>
       </c>
       <c r="BM7" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN7" s="23" t="s">
+        <v>185</v>
+      </c>
       <c r="BO7" s="23" t="s">
-        <v>70</v>
+        <v>185</v>
+      </c>
+      <c r="BP7" s="23" t="s">
+        <v>186</v>
       </c>
       <c r="BQ7" s="23" t="s">
-        <v>70</v>
+        <v>187</v>
+      </c>
+      <c r="BR7" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
@@ -2424,50 +3039,52 @@
         <v>70</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>96</v>
+        <v>188</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>70</v>
+        <v>189</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>174</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>97</v>
+        <v>191</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>70</v>
+        <v>177</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>98</v>
+        <v>192</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>99</v>
+        <v>193</v>
       </c>
       <c r="L8" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="M8" s="1"/>
+        <v>188</v>
+      </c>
+      <c r="M8" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N8" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O8" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P8" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q8" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O8" s="15">
+        <v>428292</v>
+      </c>
+      <c r="Q8" s="16">
+        <v>0</v>
       </c>
       <c r="R8" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S8" s="18" t="s">
-        <v>70</v>
+        <v>194</v>
       </c>
       <c r="T8" s="15" t="s">
         <v>70</v>
@@ -2484,9 +3101,18 @@
       <c r="X8" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="Y8" s="19">
+        <v>1</v>
+      </c>
       <c r="Z8" s="4"/>
-      <c r="AD8" s="20">
+      <c r="AA8" s="4"/>
+      <c r="AB8" s="1"/>
+      <c r="AC8" s="2"/>
+      <c r="AD8" s="19">
         <v>34</v>
+      </c>
+      <c r="AE8" s="15">
+        <v>0</v>
       </c>
       <c r="AF8" s="21">
         <v>4.7</v>
@@ -2498,8 +3124,11 @@
         <v>0</v>
       </c>
       <c r="AK8" s="1"/>
-      <c r="AL8" s="20" t="s">
-        <v>70</v>
+      <c r="AL8" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM8" s="13" t="s">
+        <v>165</v>
       </c>
       <c r="AN8" s="13" t="s">
         <v>70</v>
@@ -2507,8 +3136,14 @@
       <c r="AO8" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ8" s="20" t="s">
-        <v>70</v>
+      <c r="AP8" s="4"/>
+      <c r="AQ8" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR8" s="2"/>
+      <c r="AS8" s="1"/>
+      <c r="AT8" s="13" t="s">
+        <v>165</v>
       </c>
       <c r="AU8" s="13" t="s">
         <v>70</v>
@@ -2535,7 +3170,7 @@
         <v>70</v>
       </c>
       <c r="BC8" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BD8" s="13" t="s">
         <v>70</v>
@@ -2552,8 +3187,14 @@
       <c r="BH8" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ8" s="23" t="s">
+        <v>182</v>
+      </c>
       <c r="BK8" s="23" t="s">
-        <v>70</v>
+        <v>183</v>
+      </c>
+      <c r="BL8" s="23" t="s">
+        <v>184</v>
       </c>
       <c r="BM8" s="23" t="s">
         <v>70</v>
@@ -2568,7 +3209,7 @@
     <row r="9" ht="28" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A9" s="24"/>
       <c r="B9" s="24" t="s">
-        <v>100</v>
+        <v>195</v>
       </c>
       <c r="C9" s="24"/>
       <c r="D9" s="24"/>
@@ -2642,50 +3283,64 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" tooltip="https://www.amazon.es/dp/B0D2KT41N3"/>
-    <hyperlink ref="G2" r:id="rId2" tooltip="https://www.amazon.esundefined"/>
+    <hyperlink ref="G2" r:id="rId2" tooltip="https://www.amazon.es/stores/Cecotec/page/8A5D1609-A164-427A-9580-48312AC42537?lp_asin=B0D2KT41N3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
     <hyperlink ref="J2" r:id="rId3" tooltip="https://www.amazon.es/dp/B0D2KT41N3?psc=1"/>
-    <hyperlink ref="K2" r:id="rId4" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71zwr1xxvzL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L2" r:id="rId5" tooltip="https://www.amazon.es/dp/B0D2KT41N3"/>
-    <hyperlink ref="C3" r:id="rId6" tooltip="https://www.amazon.es/dp/B0FR4TKY99"/>
-    <hyperlink ref="G3" r:id="rId7" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J3" r:id="rId8" tooltip="https://www.amazon.es/dp/B0FR4TKY99?psc=1"/>
-    <hyperlink ref="K3" r:id="rId9" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61WbHpxBXeL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L3" r:id="rId10" tooltip="https://www.amazon.es/dp/B0FR4TKY99"/>
-    <hyperlink ref="C4" r:id="rId11" tooltip="https://www.amazon.es/dp/B0DJ7LFXC6"/>
-    <hyperlink ref="G4" r:id="rId12" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J4" r:id="rId13" tooltip="https://www.amazon.es/dp/B0DJ7LFXC6?psc=1"/>
-    <hyperlink ref="K4" r:id="rId14" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71kF7U4CGSL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L4" r:id="rId15" tooltip="https://www.amazon.es/dp/B0DJ7LFXC6"/>
-    <hyperlink ref="C5" r:id="rId16" tooltip="https://www.amazon.es/dp/B0FR44ZBJP"/>
-    <hyperlink ref="G5" r:id="rId17" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J5" r:id="rId18" tooltip="https://www.amazon.es/dp/B0FR44ZBJP?psc=1"/>
-    <hyperlink ref="K5" r:id="rId19" tooltip="https://images-eu.ssl-images-amazon.com/images/I/619yApMYqML._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L5" r:id="rId20" tooltip="https://www.amazon.es/dp/B0FR44ZBJP"/>
-    <hyperlink ref="C6" r:id="rId21" tooltip="https://www.amazon.es/dp/B0DGV9F4X3"/>
-    <hyperlink ref="G6" r:id="rId22" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J6" r:id="rId23" tooltip="https://www.amazon.es/dp/B0DGV9F4X3?psc=1"/>
-    <hyperlink ref="K6" r:id="rId24" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61ZOUuPZaJL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L6" r:id="rId25" tooltip="https://www.amazon.es/dp/B0DGV9F4X3"/>
-    <hyperlink ref="C7" r:id="rId26" tooltip="https://www.amazon.es/dp/B0H9LVZZV1"/>
-    <hyperlink ref="G7" r:id="rId27" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J7" r:id="rId28" tooltip="https://www.amazon.es/dp/B0H9LVZZV1?psc=1"/>
-    <hyperlink ref="K7" r:id="rId29" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51LLsijMWXL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L7" r:id="rId30" tooltip="https://www.amazon.es/dp/B0H9LVZZV1"/>
-    <hyperlink ref="C8" r:id="rId31" tooltip="https://www.amazon.es/dp/B0H9LQCPJ9"/>
-    <hyperlink ref="G8" r:id="rId32" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J8" r:id="rId33" tooltip="https://www.amazon.es/dp/B0H9LQCPJ9?psc=1"/>
-    <hyperlink ref="K8" r:id="rId34" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61i3ER7HQGL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L8" r:id="rId35" tooltip="https://www.amazon.es/dp/B0H9LQCPJ9"/>
+    <hyperlink ref="K2" r:id="rId4" tooltip="https://images-na.ssl-images-amazon.com/images/I/71zwr1xxvzL._AC_US600_.jpg"/>
+    <hyperlink ref="L2" r:id="rId5" tooltip="https://www.amazon.es/dp/B0D33D9J3P"/>
+    <hyperlink ref="M2" r:id="rId6" tooltip="https://www.amazon.es/b?node=218878925031"/>
+    <hyperlink ref="N2" r:id="rId7"/>
+    <hyperlink ref="C3" r:id="rId8" tooltip="https://www.amazon.es/dp/B0FR44ZBJP"/>
+    <hyperlink ref="G3" r:id="rId9" tooltip="https://www.amazon.es/stores/ROWENTA/page/3D429753-5927-4DBC-8D40-68488A481BD0?lp_asin=B0FR44ZBJP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J3" r:id="rId10" tooltip="https://www.amazon.es/dp/B0FR44ZBJP?psc=1"/>
+    <hyperlink ref="K3" r:id="rId11" tooltip="https://m.media-amazon.com/images/I/317fxQNFv3L._AC_US600_.jpg"/>
+    <hyperlink ref="L3" r:id="rId12" tooltip="https://www.amazon.es/dp/B0H633WR96"/>
+    <hyperlink ref="M3" r:id="rId13" tooltip="https://www.amazon.es/b?node=218878925031"/>
+    <hyperlink ref="N3" r:id="rId14"/>
+    <hyperlink ref="C4" r:id="rId15" tooltip="https://www.amazon.es/dp/B0FR4TKY99"/>
+    <hyperlink ref="G4" r:id="rId16" tooltip="https://www.amazon.es/stores/ROWENTA/page/3D429753-5927-4DBC-8D40-68488A481BD0?lp_asin=B0FR4TKY99&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J4" r:id="rId17" tooltip="https://www.amazon.es/dp/B0FR4TKY99?psc=1"/>
+    <hyperlink ref="K4" r:id="rId18" tooltip="https://m.media-amazon.com/images/I/31vRNmHmuqL._AC_US600_.jpg"/>
+    <hyperlink ref="L4" r:id="rId19" tooltip="https://www.amazon.es/dp/B0H63F8TQZ"/>
+    <hyperlink ref="M4" r:id="rId20" tooltip="https://www.amazon.es/b?node=218878925031"/>
+    <hyperlink ref="N4" r:id="rId21"/>
+    <hyperlink ref="C5" r:id="rId22" tooltip="https://www.amazon.es/dp/B0DJ7LFXC6"/>
+    <hyperlink ref="G5" r:id="rId23" tooltip="https://www.amazon.es/stores/roborock/page/650F9802-6540-4D28-BB83-5B16C939885D?lp_asin=B0DJ7LFXC6&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J5" r:id="rId24" tooltip="https://www.amazon.es/dp/B0DJ7LFXC6?psc=1"/>
+    <hyperlink ref="K5" r:id="rId25" tooltip="https://m.media-amazon.com/images/I/41vgb56JNJL._AC_US600_.jpg"/>
+    <hyperlink ref="L5" r:id="rId26" tooltip="https://www.amazon.es/dp/B0HDCGG5PJ"/>
+    <hyperlink ref="M5" r:id="rId27" tooltip="https://www.amazon.es/b?node=218878925031"/>
+    <hyperlink ref="N5" r:id="rId28"/>
+    <hyperlink ref="C6" r:id="rId29" tooltip="https://www.amazon.es/dp/B0DGV9F4X3"/>
+    <hyperlink ref="G6" r:id="rId30" tooltip="https://www.amazon.es/stores/ROWENTA/page/3D429753-5927-4DBC-8D40-68488A481BD0?lp_asin=B0DGV9F4X3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J6" r:id="rId31" tooltip="https://www.amazon.es/dp/B0DGV9F4X3?psc=1"/>
+    <hyperlink ref="K6" r:id="rId32" tooltip="https://images-na.ssl-images-amazon.com/images/I/61ZOUuPZaJL._AC_US600_.jpg"/>
+    <hyperlink ref="L6" r:id="rId33" tooltip="https://www.amazon.es/dp/B0DKMVFHRN"/>
+    <hyperlink ref="M6" r:id="rId34" tooltip="https://www.amazon.es/b?node=218878925031"/>
+    <hyperlink ref="N6" r:id="rId35"/>
+    <hyperlink ref="C7" r:id="rId36" tooltip="https://www.amazon.es/dp/B0H9LVZZV1"/>
+    <hyperlink ref="G7" r:id="rId37" tooltip="https://www.amazon.es/stores/BoschElectrodom%C3%A9sticos/page/2DDBCCDF-87B9-4E0B-94C6-713ED28E8982?lp_asin=B0H9LVZZV1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J7" r:id="rId38" tooltip="https://www.amazon.es/dp/B0H9LVZZV1?psc=1"/>
+    <hyperlink ref="K7" r:id="rId39" tooltip="https://images-na.ssl-images-amazon.com/images/I/51LLsijMWXL._AC_US600_.jpg"/>
+    <hyperlink ref="L7" r:id="rId40" tooltip="https://www.amazon.es/dp/B0H9LVZZV1"/>
+    <hyperlink ref="M7" r:id="rId41" tooltip="https://www.amazon.es/b?node=218878925031"/>
+    <hyperlink ref="N7" r:id="rId42"/>
+    <hyperlink ref="C8" r:id="rId43" tooltip="https://www.amazon.es/dp/B0H9LQCPJ9"/>
+    <hyperlink ref="G8" r:id="rId44" tooltip="https://www.amazon.es/stores/BoschElectrodom%C3%A9sticos/page/2DDBCCDF-87B9-4E0B-94C6-713ED28E8982?lp_asin=B0H9LQCPJ9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J8" r:id="rId45" tooltip="https://www.amazon.es/dp/B0H9LQCPJ9?psc=1"/>
+    <hyperlink ref="K8" r:id="rId46" tooltip="https://m.media-amazon.com/images/I/31jEuvrw7oL._AC_US600_.jpg"/>
+    <hyperlink ref="L8" r:id="rId47" tooltip="https://www.amazon.es/dp/B0H9LQCPJ9"/>
+    <hyperlink ref="M8" r:id="rId48" tooltip="https://www.amazon.es/b?node=218878925031"/>
+    <hyperlink ref="N8" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <drawing r:id="rId36"/>
+  <drawing r:id="rId50"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -2705,39 +3360,108 @@
         <v>21</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>101</v>
+        <v>196</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>102</v>
+        <v>197</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>104</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="B2" s="15">
-        <v>0</v>
+        <v>693</v>
       </c>
       <c r="C2" s="15">
-        <v>0</v>
+        <v>194158</v>
       </c>
       <c r="D2" s="15">
-        <v>0</v>
+        <v>4727</v>
       </c>
       <c r="E2" s="15">
-        <v>0</v>
-      </c>
-      <c r="F2" s="19">
-        <v>113.8</v>
+        <v>1324364</v>
+      </c>
+      <c r="F2" s="20">
+        <v>280.17</v>
       </c>
       <c r="G2" s="22">
-        <v>0</v>
+        <v>0.5051</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="15">
+        <v>519</v>
+      </c>
+      <c r="C3" s="15">
+        <v>19260</v>
+      </c>
+      <c r="D3" s="15">
+        <v>3653</v>
+      </c>
+      <c r="E3" s="15">
+        <v>135563</v>
+      </c>
+      <c r="F3" s="20">
+        <v>37.11</v>
+      </c>
+      <c r="G3" s="22">
+        <v>0.37829999999999997</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" s="15">
+        <v>151</v>
+      </c>
+      <c r="C4" s="15">
+        <v>32871</v>
+      </c>
+      <c r="D4" s="15">
+        <v>4449</v>
+      </c>
+      <c r="E4" s="15">
+        <v>968488</v>
+      </c>
+      <c r="F4" s="20">
+        <v>217.69</v>
+      </c>
+      <c r="G4" s="22">
+        <v>0.1101</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="15">
+        <v>9</v>
+      </c>
+      <c r="C5" s="15">
+        <v>1796</v>
+      </c>
+      <c r="D5" s="15">
+        <v>9</v>
+      </c>
+      <c r="E5" s="15">
+        <v>1796</v>
+      </c>
+      <c r="F5" s="20">
+        <v>199.5</v>
+      </c>
+      <c r="G5" s="22">
+        <v>0.0066</v>
       </c>
     </row>
   </sheetData>
@@ -2748,7 +3472,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -2759,7 +3483,7 @@
   <sheetData>
     <row r="1" ht="27" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>106</v>
+        <v>200</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>19</v>
@@ -2768,38 +3492,61 @@
         <v>21</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>101</v>
+        <v>196</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>102</v>
+        <v>197</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>104</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="B2" s="15">
+        <v>1372</v>
+      </c>
+      <c r="C2" s="15">
+        <v>313122</v>
+      </c>
+      <c r="D2" s="15">
+        <v>12838</v>
+      </c>
+      <c r="E2" s="15">
+        <v>2929931</v>
+      </c>
+      <c r="F2" s="20">
+        <v>228.22</v>
+      </c>
+      <c r="G2" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="B3" s="15">
         <v>0</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C3" s="15">
         <v>0</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D3" s="15">
         <v>0</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E3" s="15">
         <v>0</v>
       </c>
-      <c r="F2" s="19">
-        <v>113.8</v>
-      </c>
-      <c r="G2" s="22">
+      <c r="F3" s="20">
+        <v>0</v>
+      </c>
+      <c r="G3" s="22">
         <v>0</v>
       </c>
     </row>
@@ -2819,37 +3566,37 @@
   <sheetData>
     <row r="1" ht="45" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>108</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
-        <v>109</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" ht="200" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="32" t="s">
-        <v>110</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
-        <v>111</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="32" t="s">
-        <v>112</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1" spans="1:1" s="33" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="34" t="s">
-        <v>113</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
-        <v>114</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
